--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83411</v>
+        <v>83413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83413</v>
+        <v>83414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83419</v>
+        <v>83420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83420</v>
+        <v>83424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11281-2026 artfynd.xlsx
+++ b/artfynd/A 11281-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743442</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743446</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743439</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743445</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743440</v>
       </c>
       <c r="B6" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743438</v>
       </c>
       <c r="B7" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743437</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743443</v>
       </c>
       <c r="B9" t="n">
-        <v>83424</v>
+        <v>83430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743441</v>
       </c>
       <c r="B10" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743444</v>
       </c>
       <c r="B11" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
